--- a/ACME_Final_Project/Acme_Dispatcher/Data/Config.xlsx
+++ b/ACME_Final_Project/Acme_Dispatcher/Data/Config.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
